--- a/backend/data/financials_by_company/0JXL.IL.xlsx
+++ b/backend/data/financials_by_company/0JXL.IL.xlsx
@@ -692,215 +692,223 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>425508.40527</v>
+        <v>190600</v>
       </c>
       <c r="C2" t="n">
-        <v>0.102681</v>
+        <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1598000</v>
+        <v>792000</v>
       </c>
       <c r="E2" t="n">
-        <v>4144000</v>
+        <v>1906000</v>
       </c>
       <c r="F2" t="n">
-        <v>4144000</v>
+        <v>1906000</v>
       </c>
       <c r="G2" t="n">
-        <v>1983000</v>
+        <v>-151000</v>
       </c>
       <c r="H2" t="n">
-        <v>273000</v>
+        <v>565000</v>
       </c>
       <c r="I2" t="n">
-        <v>1033000</v>
+        <v>1418000</v>
       </c>
       <c r="J2" t="n">
-        <v>5742000</v>
+        <v>2698000</v>
       </c>
       <c r="K2" t="n">
-        <v>5469000</v>
+        <v>2133000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2566000</v>
+        <v>-1420000</v>
       </c>
       <c r="M2" t="n">
-        <v>3268000</v>
+        <v>2226000</v>
       </c>
       <c r="N2" t="n">
-        <v>825000</v>
+        <v>642000</v>
       </c>
       <c r="O2" t="n">
-        <v>-1735491.59473</v>
+        <v>-1866400</v>
       </c>
       <c r="P2" t="n">
-        <v>1983000</v>
+        <v>-151000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2864000</v>
+        <v>3158000</v>
       </c>
       <c r="R2" t="n">
-        <v>26000</v>
+        <v>35000</v>
       </c>
       <c r="S2" t="n">
-        <v>1625000</v>
+        <v>-578000</v>
       </c>
       <c r="T2" t="n">
-        <v>38190946</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>36852997</v>
+      </c>
+      <c r="U2" t="n">
+        <v>36852997</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.004</v>
+      </c>
       <c r="X2" t="n">
-        <v>1983000</v>
+        <v>-151000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1983000</v>
+        <v>-151000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1983000</v>
+        <v>-151000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1975000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>-158000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>1975000</v>
+        <v>-158000</v>
       </c>
       <c r="AF2" t="n">
-        <v>226000</v>
+        <v>65000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2201000</v>
+        <v>-93000</v>
       </c>
       <c r="AH2" t="n">
-        <v>384000</v>
+        <v>354000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1016000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>1755000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-1742000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>-9000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-1007000</v>
-      </c>
+        <v>-13000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>-2566000</v>
+        <v>-1420000</v>
       </c>
       <c r="AN2" t="n">
-        <v>123000</v>
+        <v>-164000</v>
       </c>
       <c r="AO2" t="n">
-        <v>3268000</v>
+        <v>2226000</v>
       </c>
       <c r="AP2" t="n">
-        <v>825000</v>
+        <v>642000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1632000</v>
+        <v>-2046000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1831000</v>
+        <v>1740000</v>
       </c>
       <c r="AS2" t="n">
-        <v>235000</v>
+        <v>153000</v>
       </c>
       <c r="AT2" t="n">
-        <v>273000</v>
+        <v>565000</v>
       </c>
       <c r="AU2" t="n">
-        <v>273000</v>
+        <v>565000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1157000</v>
+        <v>741000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1157000</v>
+        <v>741000</v>
       </c>
       <c r="AX2" t="n">
-        <v>26000</v>
+        <v>35000</v>
       </c>
       <c r="AY2" t="n">
-        <v>199000</v>
+        <v>-306000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1033000</v>
+        <v>1418000</v>
       </c>
       <c r="BA2" t="n">
-        <v>1232000</v>
+        <v>1112000</v>
       </c>
       <c r="BB2" t="n">
-        <v>1232000</v>
+        <v>1112000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>499182.679296</v>
+        <v>135005.793743</v>
       </c>
       <c r="C3" t="n">
-        <v>0.23816</v>
+        <v>0.141367</v>
       </c>
       <c r="D3" t="n">
-        <v>1648000</v>
+        <v>2328000</v>
       </c>
       <c r="E3" t="n">
-        <v>2096000</v>
+        <v>955000</v>
       </c>
       <c r="F3" t="n">
-        <v>2096000</v>
+        <v>955000</v>
       </c>
       <c r="G3" t="n">
-        <v>566000</v>
+        <v>748000</v>
       </c>
       <c r="H3" t="n">
-        <v>520000</v>
+        <v>541000</v>
       </c>
       <c r="I3" t="n">
-        <v>787000</v>
+        <v>1240000</v>
       </c>
       <c r="J3" t="n">
-        <v>3744000</v>
+        <v>3283000</v>
       </c>
       <c r="K3" t="n">
-        <v>3224000</v>
+        <v>2742000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1817000</v>
+        <v>266000</v>
       </c>
       <c r="M3" t="n">
-        <v>2485000</v>
+        <v>1879000</v>
       </c>
       <c r="N3" t="n">
-        <v>843000</v>
+        <v>80000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1030817.320704</v>
+        <v>-71994.206257</v>
       </c>
       <c r="P3" t="n">
-        <v>566000</v>
+        <v>748000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2870000</v>
+        <v>3301000</v>
       </c>
       <c r="R3" t="n">
-        <v>34000</v>
+        <v>36000</v>
       </c>
       <c r="S3" t="n">
-        <v>405000</v>
+        <v>-366000</v>
       </c>
       <c r="T3" t="n">
         <v>36852997</v>
@@ -909,158 +917,156 @@
         <v>36852997</v>
       </c>
       <c r="V3" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="X3" t="n">
-        <v>566000</v>
+        <v>748000</v>
       </c>
       <c r="Y3" t="n">
-        <v>566000</v>
+        <v>748000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>566000</v>
+        <v>748000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="AC3" t="n">
-        <v>563000</v>
+        <v>741000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>563000</v>
+        <v>741000</v>
       </c>
       <c r="AF3" t="n">
-        <v>176000</v>
+        <v>122000</v>
       </c>
       <c r="AG3" t="n">
-        <v>739000</v>
+        <v>863000</v>
       </c>
       <c r="AH3" t="n">
-        <v>206000</v>
+        <v>370000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
+        <v>-4000</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>-1817000</v>
+        <v>266000</v>
       </c>
       <c r="AN3" t="n">
-        <v>175000</v>
+        <v>-2065000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2485000</v>
+        <v>1879000</v>
       </c>
       <c r="AP3" t="n">
-        <v>843000</v>
+        <v>80000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1374000</v>
+        <v>-2182000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2083000</v>
+        <v>2061000</v>
       </c>
       <c r="AS3" t="n">
-        <v>438000</v>
+        <v>572000</v>
       </c>
       <c r="AT3" t="n">
-        <v>520000</v>
+        <v>541000</v>
       </c>
       <c r="AU3" t="n">
-        <v>520000</v>
+        <v>541000</v>
       </c>
       <c r="AV3" t="n">
-        <v>976000</v>
+        <v>706000</v>
       </c>
       <c r="AW3" t="n">
-        <v>976000</v>
+        <v>706000</v>
       </c>
       <c r="AX3" t="n">
-        <v>34000</v>
+        <v>36000</v>
       </c>
       <c r="AY3" t="n">
-        <v>709000</v>
+        <v>-121000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>787000</v>
+        <v>1240000</v>
       </c>
       <c r="BA3" t="n">
-        <v>1496000</v>
+        <v>1119000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1496000</v>
+        <v>1119000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>135005.793743</v>
+        <v>499182.679296</v>
       </c>
       <c r="C4" t="n">
-        <v>0.141367</v>
+        <v>0.23816</v>
       </c>
       <c r="D4" t="n">
-        <v>2328000</v>
+        <v>1648000</v>
       </c>
       <c r="E4" t="n">
-        <v>955000</v>
+        <v>2096000</v>
       </c>
       <c r="F4" t="n">
-        <v>955000</v>
+        <v>2096000</v>
       </c>
       <c r="G4" t="n">
-        <v>748000</v>
+        <v>566000</v>
       </c>
       <c r="H4" t="n">
-        <v>541000</v>
+        <v>520000</v>
       </c>
       <c r="I4" t="n">
-        <v>1240000</v>
+        <v>787000</v>
       </c>
       <c r="J4" t="n">
-        <v>3283000</v>
+        <v>3744000</v>
       </c>
       <c r="K4" t="n">
-        <v>2742000</v>
+        <v>3224000</v>
       </c>
       <c r="L4" t="n">
-        <v>266000</v>
+        <v>-1817000</v>
       </c>
       <c r="M4" t="n">
-        <v>1879000</v>
+        <v>2485000</v>
       </c>
       <c r="N4" t="n">
-        <v>80000</v>
+        <v>843000</v>
       </c>
       <c r="O4" t="n">
-        <v>-71994.206257</v>
+        <v>-1030817.320704</v>
       </c>
       <c r="P4" t="n">
-        <v>748000</v>
+        <v>566000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3301000</v>
+        <v>2870000</v>
       </c>
       <c r="R4" t="n">
-        <v>36000</v>
+        <v>34000</v>
       </c>
       <c r="S4" t="n">
-        <v>-366000</v>
+        <v>405000</v>
       </c>
       <c r="T4" t="n">
         <v>36852997</v>
@@ -1069,259 +1075,253 @@
         <v>36852997</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="X4" t="n">
-        <v>748000</v>
+        <v>566000</v>
       </c>
       <c r="Y4" t="n">
-        <v>748000</v>
+        <v>566000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>748000</v>
+        <v>566000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="AC4" t="n">
-        <v>741000</v>
+        <v>563000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>741000</v>
+        <v>563000</v>
       </c>
       <c r="AF4" t="n">
-        <v>122000</v>
+        <v>176000</v>
       </c>
       <c r="AG4" t="n">
-        <v>863000</v>
+        <v>739000</v>
       </c>
       <c r="AH4" t="n">
-        <v>370000</v>
+        <v>206000</v>
       </c>
       <c r="AI4" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM4" t="n">
-        <v>266000</v>
+        <v>-1817000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-2065000</v>
+        <v>175000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1879000</v>
+        <v>2485000</v>
       </c>
       <c r="AP4" t="n">
-        <v>80000</v>
+        <v>843000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2182000</v>
+        <v>-1374000</v>
       </c>
       <c r="AR4" t="n">
-        <v>2061000</v>
+        <v>2083000</v>
       </c>
       <c r="AS4" t="n">
-        <v>572000</v>
+        <v>438000</v>
       </c>
       <c r="AT4" t="n">
-        <v>541000</v>
+        <v>520000</v>
       </c>
       <c r="AU4" t="n">
-        <v>541000</v>
+        <v>520000</v>
       </c>
       <c r="AV4" t="n">
-        <v>706000</v>
+        <v>976000</v>
       </c>
       <c r="AW4" t="n">
-        <v>706000</v>
+        <v>976000</v>
       </c>
       <c r="AX4" t="n">
-        <v>36000</v>
+        <v>34000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-121000</v>
+        <v>709000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1240000</v>
+        <v>787000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1119000</v>
+        <v>1496000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1119000</v>
+        <v>1496000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>190600</v>
+        <v>425508.40527</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1</v>
+        <v>0.102681</v>
       </c>
       <c r="D5" t="n">
-        <v>792000</v>
+        <v>1598000</v>
       </c>
       <c r="E5" t="n">
-        <v>1906000</v>
+        <v>4144000</v>
       </c>
       <c r="F5" t="n">
-        <v>1906000</v>
+        <v>4144000</v>
       </c>
       <c r="G5" t="n">
-        <v>-151000</v>
+        <v>1983000</v>
       </c>
       <c r="H5" t="n">
-        <v>565000</v>
+        <v>273000</v>
       </c>
       <c r="I5" t="n">
-        <v>1418000</v>
+        <v>1033000</v>
       </c>
       <c r="J5" t="n">
-        <v>2698000</v>
+        <v>5742000</v>
       </c>
       <c r="K5" t="n">
-        <v>2133000</v>
+        <v>5469000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1420000</v>
+        <v>-2566000</v>
       </c>
       <c r="M5" t="n">
-        <v>2226000</v>
+        <v>3268000</v>
       </c>
       <c r="N5" t="n">
-        <v>642000</v>
+        <v>825000</v>
       </c>
       <c r="O5" t="n">
-        <v>-1866400</v>
+        <v>-1735491.59473</v>
       </c>
       <c r="P5" t="n">
-        <v>-151000</v>
+        <v>1983000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3158000</v>
+        <v>2864000</v>
       </c>
       <c r="R5" t="n">
-        <v>35000</v>
+        <v>26000</v>
       </c>
       <c r="S5" t="n">
-        <v>-578000</v>
+        <v>1625000</v>
       </c>
       <c r="T5" t="n">
-        <v>36852997</v>
-      </c>
-      <c r="U5" t="n">
-        <v>36852997</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.004</v>
-      </c>
+        <v>38190946</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-151000</v>
+        <v>1983000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-151000</v>
+        <v>1983000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-151000</v>
+        <v>1983000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-158000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>1975000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-158000</v>
+        <v>1975000</v>
       </c>
       <c r="AF5" t="n">
-        <v>65000</v>
+        <v>226000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-93000</v>
+        <v>2201000</v>
       </c>
       <c r="AH5" t="n">
-        <v>354000</v>
+        <v>384000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1755000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-1742000</v>
-      </c>
+        <v>1016000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>-13000</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>-9000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-1007000</v>
+      </c>
       <c r="AM5" t="n">
-        <v>-1420000</v>
+        <v>-2566000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-164000</v>
+        <v>123000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2226000</v>
+        <v>3268000</v>
       </c>
       <c r="AP5" t="n">
-        <v>642000</v>
+        <v>825000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2046000</v>
+        <v>-1632000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1740000</v>
+        <v>1831000</v>
       </c>
       <c r="AS5" t="n">
-        <v>153000</v>
+        <v>235000</v>
       </c>
       <c r="AT5" t="n">
-        <v>565000</v>
+        <v>273000</v>
       </c>
       <c r="AU5" t="n">
-        <v>565000</v>
+        <v>273000</v>
       </c>
       <c r="AV5" t="n">
-        <v>741000</v>
+        <v>1157000</v>
       </c>
       <c r="AW5" t="n">
-        <v>741000</v>
+        <v>1157000</v>
       </c>
       <c r="AX5" t="n">
-        <v>35000</v>
+        <v>26000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-306000</v>
+        <v>199000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1418000</v>
+        <v>1033000</v>
       </c>
       <c r="BA5" t="n">
-        <v>1112000</v>
+        <v>1232000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1112000</v>
+        <v>1232000</v>
       </c>
     </row>
   </sheetData>
@@ -1672,145 +1672,149 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>48764007</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>36852997</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36852997</v>
+      </c>
       <c r="D2" t="n">
-        <v>88467000</v>
+        <v>70919000</v>
       </c>
       <c r="E2" t="n">
-        <v>89044000</v>
+        <v>73276000</v>
       </c>
       <c r="F2" t="n">
-        <v>81005000</v>
+        <v>43774000</v>
       </c>
       <c r="G2" t="n">
-        <v>184670000</v>
+        <v>131798000</v>
       </c>
       <c r="H2" t="n">
-        <v>29303000</v>
+        <v>49156000</v>
       </c>
       <c r="I2" t="n">
-        <v>81005000</v>
+        <v>43774000</v>
       </c>
       <c r="J2" t="n">
-        <v>95626000</v>
+        <v>58522000</v>
       </c>
       <c r="K2" t="n">
-        <v>154059000</v>
+        <v>118261000</v>
       </c>
       <c r="L2" t="n">
-        <v>102365000</v>
+        <v>64936000</v>
       </c>
       <c r="M2" t="n">
-        <v>6739000</v>
+        <v>6414000</v>
       </c>
       <c r="N2" t="n">
-        <v>95626000</v>
+        <v>58522000</v>
       </c>
       <c r="O2" t="n">
-        <v>677000</v>
+        <v>-2620000</v>
       </c>
       <c r="P2" t="n">
-        <v>37784000</v>
+        <v>16853000</v>
       </c>
       <c r="Q2" t="n">
-        <v>48764000</v>
+        <v>36853000</v>
       </c>
       <c r="R2" t="n">
-        <v>48764000</v>
+        <v>36853000</v>
       </c>
       <c r="S2" t="n">
-        <v>96300000</v>
+        <v>75782000</v>
       </c>
       <c r="T2" t="n">
-        <v>65199000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>622000</v>
-      </c>
+        <v>61652000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>6144000</v>
+        <v>1913000</v>
       </c>
       <c r="W2" t="n">
-        <v>58433000</v>
+        <v>59739000</v>
       </c>
       <c r="X2" t="n">
-        <v>58433000</v>
+        <v>59739000</v>
       </c>
       <c r="Y2" t="n">
-        <v>31101000</v>
+        <v>14130000</v>
       </c>
       <c r="Z2" t="n">
-        <v>30611000</v>
+        <v>13537000</v>
       </c>
       <c r="AA2" t="n">
-        <v>30611000</v>
+        <v>13537000</v>
       </c>
       <c r="AB2" t="n">
-        <v>104000</v>
+        <v>164000</v>
       </c>
       <c r="AC2" t="n">
-        <v>386000</v>
+        <v>267000</v>
       </c>
       <c r="AD2" t="n">
-        <v>139000</v>
+        <v>3000</v>
       </c>
       <c r="AE2" t="n">
-        <v>49000</v>
+        <v>15000</v>
       </c>
       <c r="AF2" t="n">
-        <v>198000</v>
+        <v>249000</v>
       </c>
       <c r="AG2" t="n">
-        <v>198665000</v>
+        <v>140718000</v>
       </c>
       <c r="AH2" t="n">
-        <v>138261000</v>
+        <v>77432000</v>
       </c>
       <c r="AI2" t="n">
-        <v>576000</v>
+        <v>812000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>281000</v>
+        <v>102000</v>
       </c>
       <c r="AK2" t="n">
-        <v>9381000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>8706000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>328000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>9381000</v>
+        <v>8378000</v>
       </c>
       <c r="AN2" t="n">
-        <v>87461000</v>
+        <v>25943000</v>
       </c>
       <c r="AO2" t="n">
-        <v>14621000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>14748000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>127000</v>
+      </c>
       <c r="AQ2" t="n">
         <v>14621000</v>
       </c>
       <c r="AR2" t="n">
-        <v>25941000</v>
+        <v>27121000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-17160000</v>
+        <v>-16264000</v>
       </c>
       <c r="AT2" t="n">
-        <v>43101000</v>
+        <v>43385000</v>
       </c>
       <c r="AU2" t="n">
-        <v>13403000</v>
+        <v>13394000</v>
       </c>
       <c r="AV2" t="n">
-        <v>16921000</v>
+        <v>17802000</v>
       </c>
       <c r="AW2" t="n">
-        <v>5143000</v>
+        <v>4555000</v>
       </c>
       <c r="AX2" t="n">
         <v>7634000</v>
@@ -1819,57 +1823,57 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>60404000</v>
+        <v>63286000</v>
       </c>
       <c r="BA2" t="n">
-        <v>56000</v>
+        <v>29000</v>
       </c>
       <c r="BB2" t="n">
-        <v>668000</v>
+        <v>478000</v>
       </c>
       <c r="BC2" t="n">
-        <v>1183000</v>
+        <v>1482000</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="BE2" t="n">
         <v>5000</v>
       </c>
       <c r="BF2" t="n">
-        <v>1178000</v>
+        <v>1350000</v>
       </c>
       <c r="BG2" t="n">
-        <v>42487000</v>
+        <v>40060000</v>
       </c>
       <c r="BH2" t="n">
-        <v>22000</v>
+        <v>52000</v>
       </c>
       <c r="BI2" t="n">
-        <v>8715000</v>
+        <v>14901000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-578000</v>
+        <v>-555000</v>
       </c>
       <c r="BK2" t="n">
-        <v>9293000</v>
+        <v>15456000</v>
       </c>
       <c r="BL2" t="n">
-        <v>7273000</v>
+        <v>7072000</v>
       </c>
       <c r="BM2" t="n">
-        <v>6696000</v>
+        <v>3927000</v>
       </c>
       <c r="BN2" t="n">
-        <v>577000</v>
+        <v>2357000</v>
       </c>
       <c r="BO2" t="n">
-        <v>577000</v>
+        <v>2357000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>36852997</v>
@@ -1878,40 +1882,40 @@
         <v>36852997</v>
       </c>
       <c r="D3" t="n">
-        <v>92217000</v>
+        <v>67756000</v>
       </c>
       <c r="E3" t="n">
-        <v>92869000</v>
+        <v>68313000</v>
       </c>
       <c r="F3" t="n">
-        <v>45767000</v>
+        <v>44503000</v>
       </c>
       <c r="G3" t="n">
-        <v>153257000</v>
+        <v>127499000</v>
       </c>
       <c r="H3" t="n">
-        <v>50244000</v>
+        <v>44016000</v>
       </c>
       <c r="I3" t="n">
-        <v>45767000</v>
+        <v>44503000</v>
       </c>
       <c r="J3" t="n">
-        <v>60388000</v>
+        <v>59186000</v>
       </c>
       <c r="K3" t="n">
-        <v>137851000</v>
+        <v>113032000</v>
       </c>
       <c r="L3" t="n">
-        <v>67472000</v>
+        <v>65593000</v>
       </c>
       <c r="M3" t="n">
-        <v>7084000</v>
+        <v>6407000</v>
       </c>
       <c r="N3" t="n">
-        <v>60388000</v>
+        <v>59186000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1306000</v>
+        <v>-1872000</v>
       </c>
       <c r="P3" t="n">
         <v>16853000</v>
@@ -1923,90 +1927,92 @@
         <v>36853000</v>
       </c>
       <c r="S3" t="n">
-        <v>96385000</v>
+        <v>71531000</v>
       </c>
       <c r="T3" t="n">
-        <v>80522000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>768000</v>
-      </c>
+        <v>55920000</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>2291000</v>
+        <v>2074000</v>
       </c>
       <c r="W3" t="n">
-        <v>77463000</v>
+        <v>53846000</v>
       </c>
       <c r="X3" t="n">
-        <v>77463000</v>
+        <v>53846000</v>
       </c>
       <c r="Y3" t="n">
-        <v>15863000</v>
+        <v>15611000</v>
       </c>
       <c r="Z3" t="n">
-        <v>15406000</v>
+        <v>14467000</v>
       </c>
       <c r="AA3" t="n">
-        <v>15406000</v>
+        <v>14467000</v>
       </c>
       <c r="AB3" t="n">
-        <v>51000</v>
+        <v>118000</v>
       </c>
       <c r="AC3" t="n">
-        <v>247000</v>
+        <v>864000</v>
       </c>
       <c r="AD3" t="n">
-        <v>35000</v>
+        <v>25000</v>
       </c>
       <c r="AE3" t="n">
-        <v>16000</v>
+        <v>49000</v>
       </c>
       <c r="AF3" t="n">
-        <v>196000</v>
+        <v>790000</v>
       </c>
       <c r="AG3" t="n">
-        <v>163857000</v>
+        <v>137124000</v>
       </c>
       <c r="AH3" t="n">
-        <v>97750000</v>
+        <v>77497000</v>
       </c>
       <c r="AI3" t="n">
-        <v>18779000</v>
+        <v>37000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>246000</v>
+        <v>209000</v>
       </c>
       <c r="AK3" t="n">
-        <v>8926000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>8515000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" t="n">
-        <v>8926000</v>
+        <v>8515000</v>
       </c>
       <c r="AN3" t="n">
-        <v>28967000</v>
+        <v>27393000</v>
       </c>
       <c r="AO3" t="n">
-        <v>14621000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>14683000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>62000</v>
+      </c>
       <c r="AQ3" t="n">
         <v>14621000</v>
       </c>
       <c r="AR3" t="n">
-        <v>26211000</v>
+        <v>26660000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-16869000</v>
+        <v>-16447000</v>
       </c>
       <c r="AT3" t="n">
-        <v>43080000</v>
+        <v>43107000</v>
       </c>
       <c r="AU3" t="n">
-        <v>13398000</v>
+        <v>13405000</v>
       </c>
       <c r="AV3" t="n">
-        <v>16905000</v>
+        <v>16925000</v>
       </c>
       <c r="AW3" t="n">
         <v>5143000</v>
@@ -2018,16 +2024,16 @@
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>66107000</v>
+        <v>59627000</v>
       </c>
       <c r="BA3" t="n">
-        <v>25000</v>
+        <v>9000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1618000</v>
+        <v>477000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1362000</v>
+        <v>1480000</v>
       </c>
       <c r="BD3" t="n">
         <v>127000</v>
@@ -2036,39 +2042,39 @@
         <v>5000</v>
       </c>
       <c r="BF3" t="n">
-        <v>1230000</v>
+        <v>1348000</v>
       </c>
       <c r="BG3" t="n">
-        <v>43711000</v>
+        <v>45331000</v>
       </c>
       <c r="BH3" t="n">
-        <v>8000</v>
+        <v>14000</v>
       </c>
       <c r="BI3" t="n">
-        <v>10277000</v>
+        <v>6321000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-628000</v>
+        <v>-1078000</v>
       </c>
       <c r="BK3" t="n">
-        <v>10905000</v>
+        <v>7399000</v>
       </c>
       <c r="BL3" t="n">
-        <v>9106000</v>
+        <v>5995000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8454000</v>
+        <v>5438000</v>
       </c>
       <c r="BN3" t="n">
-        <v>652000</v>
+        <v>557000</v>
       </c>
       <c r="BO3" t="n">
-        <v>652000</v>
+        <v>557000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>36852997</v>
@@ -2077,40 +2083,40 @@
         <v>36852997</v>
       </c>
       <c r="D4" t="n">
-        <v>67756000</v>
+        <v>92217000</v>
       </c>
       <c r="E4" t="n">
-        <v>68313000</v>
+        <v>92869000</v>
       </c>
       <c r="F4" t="n">
-        <v>44503000</v>
+        <v>45767000</v>
       </c>
       <c r="G4" t="n">
-        <v>127499000</v>
+        <v>153257000</v>
       </c>
       <c r="H4" t="n">
-        <v>44016000</v>
+        <v>50244000</v>
       </c>
       <c r="I4" t="n">
-        <v>44503000</v>
+        <v>45767000</v>
       </c>
       <c r="J4" t="n">
-        <v>59186000</v>
+        <v>60388000</v>
       </c>
       <c r="K4" t="n">
-        <v>113032000</v>
+        <v>137851000</v>
       </c>
       <c r="L4" t="n">
-        <v>65593000</v>
+        <v>67472000</v>
       </c>
       <c r="M4" t="n">
-        <v>6407000</v>
+        <v>7084000</v>
       </c>
       <c r="N4" t="n">
-        <v>59186000</v>
+        <v>60388000</v>
       </c>
       <c r="O4" t="n">
-        <v>-1872000</v>
+        <v>-1306000</v>
       </c>
       <c r="P4" t="n">
         <v>16853000</v>
@@ -2122,92 +2128,90 @@
         <v>36853000</v>
       </c>
       <c r="S4" t="n">
-        <v>71531000</v>
+        <v>96385000</v>
       </c>
       <c r="T4" t="n">
-        <v>55920000</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>80522000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>768000</v>
+      </c>
       <c r="V4" t="n">
-        <v>2074000</v>
+        <v>2291000</v>
       </c>
       <c r="W4" t="n">
-        <v>53846000</v>
+        <v>77463000</v>
       </c>
       <c r="X4" t="n">
-        <v>53846000</v>
+        <v>77463000</v>
       </c>
       <c r="Y4" t="n">
-        <v>15611000</v>
+        <v>15863000</v>
       </c>
       <c r="Z4" t="n">
-        <v>14467000</v>
+        <v>15406000</v>
       </c>
       <c r="AA4" t="n">
-        <v>14467000</v>
+        <v>15406000</v>
       </c>
       <c r="AB4" t="n">
-        <v>118000</v>
+        <v>51000</v>
       </c>
       <c r="AC4" t="n">
-        <v>864000</v>
+        <v>247000</v>
       </c>
       <c r="AD4" t="n">
-        <v>25000</v>
+        <v>35000</v>
       </c>
       <c r="AE4" t="n">
-        <v>49000</v>
+        <v>16000</v>
       </c>
       <c r="AF4" t="n">
-        <v>790000</v>
+        <v>196000</v>
       </c>
       <c r="AG4" t="n">
-        <v>137124000</v>
+        <v>163857000</v>
       </c>
       <c r="AH4" t="n">
-        <v>77497000</v>
+        <v>97750000</v>
       </c>
       <c r="AI4" t="n">
-        <v>37000</v>
+        <v>18779000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>209000</v>
+        <v>246000</v>
       </c>
       <c r="AK4" t="n">
-        <v>8515000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>8926000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>8515000</v>
+        <v>8926000</v>
       </c>
       <c r="AN4" t="n">
-        <v>27393000</v>
+        <v>28967000</v>
       </c>
       <c r="AO4" t="n">
-        <v>14683000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>62000</v>
-      </c>
+        <v>14621000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
         <v>14621000</v>
       </c>
       <c r="AR4" t="n">
-        <v>26660000</v>
+        <v>26211000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-16447000</v>
+        <v>-16869000</v>
       </c>
       <c r="AT4" t="n">
-        <v>43107000</v>
+        <v>43080000</v>
       </c>
       <c r="AU4" t="n">
-        <v>13405000</v>
+        <v>13398000</v>
       </c>
       <c r="AV4" t="n">
-        <v>16925000</v>
+        <v>16905000</v>
       </c>
       <c r="AW4" t="n">
         <v>5143000</v>
@@ -2219,16 +2223,16 @@
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>59627000</v>
+        <v>66107000</v>
       </c>
       <c r="BA4" t="n">
-        <v>9000</v>
+        <v>25000</v>
       </c>
       <c r="BB4" t="n">
-        <v>477000</v>
+        <v>1618000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1480000</v>
+        <v>1362000</v>
       </c>
       <c r="BD4" t="n">
         <v>127000</v>
@@ -2237,181 +2241,177 @@
         <v>5000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1348000</v>
+        <v>1230000</v>
       </c>
       <c r="BG4" t="n">
-        <v>45331000</v>
+        <v>43711000</v>
       </c>
       <c r="BH4" t="n">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="BI4" t="n">
-        <v>6321000</v>
+        <v>10277000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-1078000</v>
+        <v>-628000</v>
       </c>
       <c r="BK4" t="n">
-        <v>7399000</v>
+        <v>10905000</v>
       </c>
       <c r="BL4" t="n">
-        <v>5995000</v>
+        <v>9106000</v>
       </c>
       <c r="BM4" t="n">
-        <v>5438000</v>
+        <v>8454000</v>
       </c>
       <c r="BN4" t="n">
-        <v>557000</v>
+        <v>652000</v>
       </c>
       <c r="BO4" t="n">
-        <v>557000</v>
+        <v>652000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>36852997</v>
-      </c>
-      <c r="C5" t="n">
-        <v>36852997</v>
-      </c>
+        <v>48764007</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>70919000</v>
+        <v>88467000</v>
       </c>
       <c r="E5" t="n">
-        <v>73276000</v>
+        <v>89044000</v>
       </c>
       <c r="F5" t="n">
-        <v>43774000</v>
+        <v>81005000</v>
       </c>
       <c r="G5" t="n">
-        <v>131798000</v>
+        <v>184670000</v>
       </c>
       <c r="H5" t="n">
-        <v>49156000</v>
+        <v>29303000</v>
       </c>
       <c r="I5" t="n">
-        <v>43774000</v>
+        <v>81005000</v>
       </c>
       <c r="J5" t="n">
-        <v>58522000</v>
+        <v>95626000</v>
       </c>
       <c r="K5" t="n">
-        <v>118261000</v>
+        <v>154059000</v>
       </c>
       <c r="L5" t="n">
-        <v>64936000</v>
+        <v>102365000</v>
       </c>
       <c r="M5" t="n">
-        <v>6414000</v>
+        <v>6739000</v>
       </c>
       <c r="N5" t="n">
-        <v>58522000</v>
+        <v>95626000</v>
       </c>
       <c r="O5" t="n">
-        <v>-2620000</v>
+        <v>677000</v>
       </c>
       <c r="P5" t="n">
-        <v>16853000</v>
+        <v>37784000</v>
       </c>
       <c r="Q5" t="n">
-        <v>36853000</v>
+        <v>48764000</v>
       </c>
       <c r="R5" t="n">
-        <v>36853000</v>
+        <v>48764000</v>
       </c>
       <c r="S5" t="n">
-        <v>75782000</v>
+        <v>96300000</v>
       </c>
       <c r="T5" t="n">
-        <v>61652000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>65199000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>622000</v>
+      </c>
       <c r="V5" t="n">
-        <v>1913000</v>
+        <v>6144000</v>
       </c>
       <c r="W5" t="n">
-        <v>59739000</v>
+        <v>58433000</v>
       </c>
       <c r="X5" t="n">
-        <v>59739000</v>
+        <v>58433000</v>
       </c>
       <c r="Y5" t="n">
-        <v>14130000</v>
+        <v>31101000</v>
       </c>
       <c r="Z5" t="n">
-        <v>13537000</v>
+        <v>30611000</v>
       </c>
       <c r="AA5" t="n">
-        <v>13537000</v>
+        <v>30611000</v>
       </c>
       <c r="AB5" t="n">
-        <v>164000</v>
+        <v>104000</v>
       </c>
       <c r="AC5" t="n">
-        <v>267000</v>
+        <v>386000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3000</v>
+        <v>139000</v>
       </c>
       <c r="AE5" t="n">
-        <v>15000</v>
+        <v>49000</v>
       </c>
       <c r="AF5" t="n">
-        <v>249000</v>
+        <v>198000</v>
       </c>
       <c r="AG5" t="n">
-        <v>140718000</v>
+        <v>198665000</v>
       </c>
       <c r="AH5" t="n">
-        <v>77432000</v>
+        <v>138261000</v>
       </c>
       <c r="AI5" t="n">
-        <v>812000</v>
+        <v>576000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>102000</v>
+        <v>281000</v>
       </c>
       <c r="AK5" t="n">
-        <v>8706000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>328000</v>
-      </c>
+        <v>9381000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>8378000</v>
+        <v>9381000</v>
       </c>
       <c r="AN5" t="n">
-        <v>25943000</v>
+        <v>87461000</v>
       </c>
       <c r="AO5" t="n">
-        <v>14748000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>127000</v>
-      </c>
+        <v>14621000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
         <v>14621000</v>
       </c>
       <c r="AR5" t="n">
-        <v>27121000</v>
+        <v>25941000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-16264000</v>
+        <v>-17160000</v>
       </c>
       <c r="AT5" t="n">
-        <v>43385000</v>
+        <v>43101000</v>
       </c>
       <c r="AU5" t="n">
-        <v>13394000</v>
+        <v>13403000</v>
       </c>
       <c r="AV5" t="n">
-        <v>17802000</v>
+        <v>16921000</v>
       </c>
       <c r="AW5" t="n">
-        <v>4555000</v>
+        <v>5143000</v>
       </c>
       <c r="AX5" t="n">
         <v>7634000</v>
@@ -2420,52 +2420,52 @@
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>63286000</v>
+        <v>60404000</v>
       </c>
       <c r="BA5" t="n">
-        <v>29000</v>
+        <v>56000</v>
       </c>
       <c r="BB5" t="n">
-        <v>478000</v>
+        <v>668000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1482000</v>
+        <v>1183000</v>
       </c>
       <c r="BD5" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>5000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1350000</v>
+        <v>1178000</v>
       </c>
       <c r="BG5" t="n">
-        <v>40060000</v>
+        <v>42487000</v>
       </c>
       <c r="BH5" t="n">
-        <v>52000</v>
+        <v>22000</v>
       </c>
       <c r="BI5" t="n">
-        <v>14901000</v>
+        <v>8715000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-555000</v>
+        <v>-578000</v>
       </c>
       <c r="BK5" t="n">
-        <v>15456000</v>
+        <v>9293000</v>
       </c>
       <c r="BL5" t="n">
-        <v>7072000</v>
+        <v>7273000</v>
       </c>
       <c r="BM5" t="n">
-        <v>3927000</v>
+        <v>6696000</v>
       </c>
       <c r="BN5" t="n">
-        <v>2357000</v>
+        <v>577000</v>
       </c>
       <c r="BO5" t="n">
-        <v>2357000</v>
+        <v>577000</v>
       </c>
     </row>
   </sheetData>
@@ -2661,430 +2661,430 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-928000</v>
+        <v>1595000</v>
       </c>
       <c r="C2" t="n">
-        <v>-12378000</v>
+        <v>-42205000</v>
       </c>
       <c r="D2" t="n">
-        <v>8214000</v>
+        <v>38680000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3000</v>
+        <v>-76000</v>
       </c>
       <c r="F2" t="n">
-        <v>577000</v>
+        <v>2357000</v>
       </c>
       <c r="G2" t="n">
-        <v>652000</v>
+        <v>3558000</v>
       </c>
       <c r="H2" t="n">
-        <v>-75000</v>
+        <v>-1201000</v>
       </c>
       <c r="I2" t="n">
-        <v>-7970000</v>
+        <v>-5555000</v>
       </c>
       <c r="J2" t="n">
-        <v>-128000</v>
+        <v>-180000</v>
       </c>
       <c r="K2" t="n">
-        <v>-3678000</v>
+        <v>-1850000</v>
       </c>
       <c r="L2" t="n">
-        <v>-4164000</v>
+        <v>-3525000</v>
       </c>
       <c r="M2" t="n">
-        <v>-4164000</v>
+        <v>-3525000</v>
       </c>
       <c r="N2" t="n">
-        <v>-12378000</v>
+        <v>-42205000</v>
       </c>
       <c r="O2" t="n">
-        <v>8214000</v>
+        <v>38680000</v>
       </c>
       <c r="P2" t="n">
-        <v>8820000</v>
+        <v>2683000</v>
       </c>
       <c r="Q2" t="n">
-        <v>205000</v>
+        <v>98000</v>
       </c>
       <c r="R2" t="n">
-        <v>22000</v>
+        <v>353000</v>
       </c>
       <c r="S2" t="n">
-        <v>9057000</v>
+        <v>-2558000</v>
       </c>
       <c r="T2" t="n">
-        <v>9994000</v>
+        <v>34424000</v>
       </c>
       <c r="U2" t="n">
-        <v>-937000</v>
+        <v>-36982000</v>
       </c>
       <c r="V2" t="n">
-        <v>-486000</v>
+        <v>4746000</v>
       </c>
       <c r="W2" t="n">
-        <v>14000</v>
+        <v>5485000</v>
       </c>
       <c r="X2" t="n">
-        <v>-500000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>-739000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-4000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-3000</v>
+        <v>-72000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3000</v>
+        <v>-72000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-925000</v>
+        <v>1671000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-64000</v>
+        <v>-142000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2139000</v>
+        <v>-3987000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-135000</v>
+        <v>-231000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-893000</v>
+        <v>-1573000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1111000</v>
+        <v>-2183000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1278000</v>
+        <v>5800000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1278000</v>
+        <v>5800000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-728000</v>
+        <v>-1194000</v>
       </c>
       <c r="C3" t="n">
-        <v>-17878000</v>
+        <v>-24697000</v>
       </c>
       <c r="D3" t="n">
-        <v>42104000</v>
+        <v>19353000</v>
       </c>
       <c r="E3" t="n">
-        <v>-30000</v>
+        <v>-26000</v>
       </c>
       <c r="F3" t="n">
-        <v>652000</v>
+        <v>557000</v>
       </c>
       <c r="G3" t="n">
-        <v>557000</v>
+        <v>2357000</v>
       </c>
       <c r="H3" t="n">
-        <v>95000</v>
+        <v>-1800000</v>
       </c>
       <c r="I3" t="n">
-        <v>22204000</v>
+        <v>-7054000</v>
       </c>
       <c r="J3" t="n">
-        <v>-132000</v>
+        <v>-128000</v>
       </c>
       <c r="K3" t="n">
-        <v>-1890000</v>
+        <v>-1582000</v>
       </c>
       <c r="L3" t="n">
-        <v>24226000</v>
+        <v>-5344000</v>
       </c>
       <c r="M3" t="n">
-        <v>24226000</v>
+        <v>-5344000</v>
       </c>
       <c r="N3" t="n">
-        <v>-17878000</v>
+        <v>-24697000</v>
       </c>
       <c r="O3" t="n">
-        <v>42104000</v>
+        <v>19353000</v>
       </c>
       <c r="P3" t="n">
-        <v>-21411000</v>
+        <v>6422000</v>
       </c>
       <c r="Q3" t="n">
-        <v>49000</v>
+        <v>78000</v>
       </c>
       <c r="R3" t="n">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="S3" t="n">
-        <v>-4007000</v>
+        <v>5026000</v>
       </c>
       <c r="T3" t="n">
-        <v>8474000</v>
+        <v>10448000</v>
       </c>
       <c r="U3" t="n">
-        <v>-12481000</v>
+        <v>-5422000</v>
       </c>
       <c r="V3" t="n">
-        <v>-18000000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
-        <v>-18000000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+        <v>939000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>939000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>-30000</v>
+        <v>-26000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-30000</v>
+        <v>-26000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-698000</v>
+        <v>-1168000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-165000</v>
+        <v>-68000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2136000</v>
+        <v>-2241000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-209000</v>
+        <v>-184000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-848000</v>
+        <v>-1318000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1079000</v>
+        <v>-739000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1603000</v>
+        <v>1141000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1603000</v>
+        <v>1141000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1194000</v>
+        <v>-728000</v>
       </c>
       <c r="C4" t="n">
-        <v>-24697000</v>
+        <v>-17878000</v>
       </c>
       <c r="D4" t="n">
-        <v>19353000</v>
+        <v>42104000</v>
       </c>
       <c r="E4" t="n">
-        <v>-26000</v>
+        <v>-30000</v>
       </c>
       <c r="F4" t="n">
+        <v>652000</v>
+      </c>
+      <c r="G4" t="n">
         <v>557000</v>
       </c>
-      <c r="G4" t="n">
-        <v>2357000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-1800000</v>
+        <v>95000</v>
       </c>
       <c r="I4" t="n">
-        <v>-7054000</v>
+        <v>22204000</v>
       </c>
       <c r="J4" t="n">
-        <v>-128000</v>
+        <v>-132000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1582000</v>
+        <v>-1890000</v>
       </c>
       <c r="L4" t="n">
-        <v>-5344000</v>
+        <v>24226000</v>
       </c>
       <c r="M4" t="n">
-        <v>-5344000</v>
+        <v>24226000</v>
       </c>
       <c r="N4" t="n">
-        <v>-24697000</v>
+        <v>-17878000</v>
       </c>
       <c r="O4" t="n">
-        <v>19353000</v>
+        <v>42104000</v>
       </c>
       <c r="P4" t="n">
-        <v>6422000</v>
+        <v>-21411000</v>
       </c>
       <c r="Q4" t="n">
-        <v>78000</v>
+        <v>49000</v>
       </c>
       <c r="R4" t="n">
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="S4" t="n">
-        <v>5026000</v>
+        <v>-4007000</v>
       </c>
       <c r="T4" t="n">
-        <v>10448000</v>
+        <v>8474000</v>
       </c>
       <c r="U4" t="n">
-        <v>-5422000</v>
+        <v>-12481000</v>
       </c>
       <c r="V4" t="n">
-        <v>939000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>939000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+        <v>-18000000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>-18000000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-26000</v>
+        <v>-30000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-26000</v>
+        <v>-30000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1168000</v>
+        <v>-698000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-68000</v>
+        <v>-165000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2241000</v>
+        <v>-2136000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-184000</v>
+        <v>-209000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1318000</v>
+        <v>-848000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-739000</v>
+        <v>-1079000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1141000</v>
+        <v>1603000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1141000</v>
+        <v>1603000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1595000</v>
+        <v>-928000</v>
       </c>
       <c r="C5" t="n">
-        <v>-42205000</v>
+        <v>-12378000</v>
       </c>
       <c r="D5" t="n">
-        <v>38680000</v>
+        <v>8214000</v>
       </c>
       <c r="E5" t="n">
-        <v>-76000</v>
+        <v>-3000</v>
       </c>
       <c r="F5" t="n">
-        <v>2357000</v>
+        <v>577000</v>
       </c>
       <c r="G5" t="n">
-        <v>3558000</v>
+        <v>652000</v>
       </c>
       <c r="H5" t="n">
-        <v>-1201000</v>
+        <v>-75000</v>
       </c>
       <c r="I5" t="n">
-        <v>-5555000</v>
+        <v>-7970000</v>
       </c>
       <c r="J5" t="n">
-        <v>-180000</v>
+        <v>-128000</v>
       </c>
       <c r="K5" t="n">
-        <v>-1850000</v>
+        <v>-3678000</v>
       </c>
       <c r="L5" t="n">
-        <v>-3525000</v>
+        <v>-4164000</v>
       </c>
       <c r="M5" t="n">
-        <v>-3525000</v>
+        <v>-4164000</v>
       </c>
       <c r="N5" t="n">
-        <v>-42205000</v>
+        <v>-12378000</v>
       </c>
       <c r="O5" t="n">
-        <v>38680000</v>
+        <v>8214000</v>
       </c>
       <c r="P5" t="n">
-        <v>2683000</v>
+        <v>8820000</v>
       </c>
       <c r="Q5" t="n">
-        <v>98000</v>
+        <v>205000</v>
       </c>
       <c r="R5" t="n">
-        <v>353000</v>
+        <v>22000</v>
       </c>
       <c r="S5" t="n">
-        <v>-2558000</v>
+        <v>9057000</v>
       </c>
       <c r="T5" t="n">
-        <v>34424000</v>
+        <v>9994000</v>
       </c>
       <c r="U5" t="n">
-        <v>-36982000</v>
+        <v>-937000</v>
       </c>
       <c r="V5" t="n">
-        <v>4746000</v>
+        <v>-486000</v>
       </c>
       <c r="W5" t="n">
-        <v>5485000</v>
+        <v>14000</v>
       </c>
       <c r="X5" t="n">
-        <v>-739000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-4000</v>
-      </c>
+        <v>-500000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-72000</v>
+        <v>-3000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-72000</v>
+        <v>-3000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1671000</v>
+        <v>-925000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-142000</v>
+        <v>-64000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3987000</v>
+        <v>-2139000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-231000</v>
+        <v>-135000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1573000</v>
+        <v>-893000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2183000</v>
+        <v>-1111000</v>
       </c>
       <c r="AI5" t="n">
-        <v>5800000</v>
+        <v>1278000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5800000</v>
+        <v>1278000</v>
       </c>
     </row>
   </sheetData>
@@ -3149,192 +3149,192 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>tradeable</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>regularMarketPreviousClose</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume10Day</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLow</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHigh</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverage</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverage</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>priceHint</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverage</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverage</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>tradeable</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>regularMarketPreviousClose</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume10Day</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLow</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHigh</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
@@ -3387,63 +3387,59 @@
           <t>BGN</t>
         </is>
       </c>
-      <c r="J2" t="b">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0JXL.IL,0P0000KJY1,0</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>1518768000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1721764800</v>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>IOB</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Europe/London</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>BST</t>
-        </is>
-      </c>
       <c r="R2" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>gb_market</t>
-        </is>
-      </c>
-      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" t="n">
-        <v>2.16</v>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2.16 - 2.16</t>
+        </is>
       </c>
       <c r="W2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z2" t="n">
         <v>2.16</v>
@@ -3452,72 +3448,76 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>15</v>
-      </c>
       <c r="AD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="b">
+      <c r="AE2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>1721764800</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>IOB</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>BST</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>gb_market</t>
+        </is>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="AQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1518768000000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
         <v>2.16</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>IOB</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2.16 - 2.16</t>
-        </is>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0JXL.IL,0P0000KJY1,0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>POSTPOST</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr"/>
     </row>
